--- a/gantt-piloto-2026-10-29.xlsx
+++ b/gantt-piloto-2026-10-29.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="355">
   <si>
     <t xml:space="preserve">Grupo Bimbo × Uvicuo · Plan de arranque del piloto de peajes</t>
   </si>
@@ -359,7 +359,10 @@
     <t xml:space="preserve">Sesión con Tesorería y Televía para capturar las tarjetas, convocada</t>
   </si>
   <si>
-    <t xml:space="preserve">Sesión agendada con Tesorería, Televía y Uvicuo para capturar la tarjeta de Bimbo y la de Barcel en su cuenta de Televía.</t>
+    <t xml:space="preserve">Sesión con Tesorería y Televía: la de Barcel quedó agendada para el viernes 30 de octubre; falta agendar la de Bimbo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En curso</t>
   </si>
   <si>
     <t xml:space="preserve">● 1.5.2</t>
@@ -497,9 +500,6 @@
     <t xml:space="preserve">Instructivo de pegado para los tractos, alineado a la guía vigente de Televía.</t>
   </si>
   <si>
-    <t xml:space="preserve">En curso</t>
-  </si>
-  <si>
     <t xml:space="preserve">3.2.1</t>
   </si>
   <si>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">Equipo de monitoreo de Televía para el arranque, confirmado</t>
   </si>
   <si>
-    <t xml:space="preserve">Un equipo de Televía monitoreando las rutas del piloto desde el primer cruce (3 de noviembre), con un contacto que resuelve en el momento si un tag se rechaza.</t>
+    <t xml:space="preserve">Un equipo de Televía monitoreando las rutas del piloto desde el primer cruce (4 de noviembre), con un contacto que resuelve en el momento si un tag se rechaza.</t>
   </si>
   <si>
     <t xml:space="preserve">3.3.6 · 3.3.7</t>
@@ -1136,10 +1136,10 @@
     <t xml:space="preserve">Grupo Bimbo · Tesorería</t>
   </si>
   <si>
-    <t xml:space="preserve">A más tardar el lunes 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Es la compuerta del arranque: con ellas el primer cruce es el martes 3 (Bimbo) y el miércoles 4 (Barcel)</t>
+    <t xml:space="preserve">A más tardar el martes 3 de noviembre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es la compuerta del arranque: con ellas el primer cruce (controlado) es el miércoles 4 de noviembre y el piloto arranca el lunes 9</t>
   </si>
   <si>
     <t xml:space="preserve">Visto bueno de los criterios de éxito de las dos operaciones</t>
@@ -4010,12 +4010,12 @@
       </c>
       <c r="M13" s="24" t="n">
         <f aca="false">IF(AND(ISNUMBER(L13),ISNUMBER(O13)),O13-L13+1,"")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N13" s="23"/>
       <c r="O13" s="23" t="n">
         <f aca="false">IF(COUNT(O14,O15,O16,O17)=0,"",MAX(O14,O15,O16,O17))</f>
-        <v>46329</v>
+        <v>46330</v>
       </c>
       <c r="P13" s="22"/>
       <c r="Q13" s="17"/>
@@ -4103,7 +4103,7 @@
         <v>31</v>
       </c>
       <c r="I14" s="22" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J14" s="19"/>
       <c r="K14" s="15" t="s">
@@ -4190,22 +4190,22 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="2" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B15" s="16"/>
       <c r="C15" s="33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D15" s="17"/>
       <c r="E15" s="18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F15" s="19"/>
       <c r="G15" s="20" t="s">
         <v>30</v>
       </c>
       <c r="H15" s="21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I15" s="22" t="s">
         <v>54</v>
@@ -4215,7 +4215,7 @@
         <v>40</v>
       </c>
       <c r="L15" s="23" t="n">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="M15" s="24" t="n">
         <v>1</v>
@@ -4223,7 +4223,7 @@
       <c r="N15" s="23"/>
       <c r="O15" s="23" t="n">
         <f aca="false">IF(ISNUMBER(L15),L15+M15-1,"")</f>
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="P15" s="22" t="s">
         <v>41</v>
@@ -4295,22 +4295,22 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="2" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B16" s="16"/>
       <c r="C16" s="33" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D16" s="17"/>
       <c r="E16" s="18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F16" s="19"/>
       <c r="G16" s="20" t="s">
         <v>30</v>
       </c>
       <c r="H16" s="21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I16" s="22" t="s">
         <v>54</v>
@@ -4320,7 +4320,7 @@
         <v>40</v>
       </c>
       <c r="L16" s="23" t="n">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="M16" s="24" t="n">
         <v>1</v>
@@ -4328,7 +4328,7 @@
       <c r="N16" s="23"/>
       <c r="O16" s="23" t="n">
         <f aca="false">IF(ISNUMBER(L16),L16+M16-1,"")</f>
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="P16" s="22" t="s">
         <v>41</v>
@@ -4400,19 +4400,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="2" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B17" s="16"/>
       <c r="C17" s="33" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D17" s="17"/>
       <c r="E17" s="18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F17" s="19"/>
       <c r="G17" s="30" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H17" s="21" t="s">
         <v>31</v>
@@ -4421,14 +4421,14 @@
         <v>54</v>
       </c>
       <c r="J17" s="34" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K17" s="15" t="s">
         <v>40</v>
       </c>
       <c r="L17" s="23" t="n">
-        <f aca="false">MAX(DATE(2026,11,3),IF(COUNT(O15,O16)=0,0,MAX(O15,O16)+1))</f>
-        <v>46329</v>
+        <f aca="false">MAX(DATE(2026,11,4),IF(COUNT(O15,O16)=0,0,MAX(O15,O16)+1))</f>
+        <v>46330</v>
       </c>
       <c r="M17" s="24" t="n">
         <v>1</v>
@@ -4436,7 +4436,7 @@
       <c r="N17" s="23"/>
       <c r="O17" s="23" t="n">
         <f aca="false">IF(ISNUMBER(L17),L17+M17-1,"")</f>
-        <v>46329</v>
+        <v>46330</v>
       </c>
       <c r="P17" s="22" t="s">
         <v>41</v>
@@ -4508,10 +4508,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="35" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C18" s="37"/>
       <c r="D18" s="37"/>
@@ -4873,7 +4873,7 @@
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
@@ -4957,29 +4957,29 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C21" s="17"/>
       <c r="D21" s="17"/>
       <c r="E21" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F21" s="19"/>
       <c r="G21" s="20" t="s">
         <v>30</v>
       </c>
       <c r="H21" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I21" s="22" t="s">
         <v>32</v>
       </c>
       <c r="J21" s="19"/>
       <c r="K21" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L21" s="23" t="n">
         <v>46316</v>
@@ -5061,15 +5061,15 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C22" s="17"/>
       <c r="D22" s="17"/>
       <c r="E22" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F22" s="19"/>
       <c r="G22" s="20" t="s">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="J22" s="19"/>
       <c r="K22" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L22" s="23" t="n">
         <v>46316</v>
@@ -5165,15 +5165,15 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="17"/>
       <c r="E23" s="18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F23" s="19"/>
       <c r="G23" s="20" t="s">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="J23" s="19"/>
       <c r="K23" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L23" s="23" t="n">
         <v>46316</v>
@@ -5269,15 +5269,15 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C24" s="17"/>
       <c r="D24" s="17"/>
       <c r="E24" s="18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F24" s="19"/>
       <c r="G24" s="20" t="s">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="J24" s="19"/>
       <c r="K24" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L24" s="23" t="n">
         <v>46316</v>
@@ -5373,29 +5373,29 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C25" s="17"/>
       <c r="D25" s="17"/>
       <c r="E25" s="18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F25" s="19"/>
       <c r="G25" s="30" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H25" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I25" s="22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J25" s="19"/>
       <c r="K25" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L25" s="23" t="n">
         <f aca="false">MAX(DATE(2026,10,21),IF(COUNT(O24)=0,0,MAX(O24)+1))</f>
@@ -5478,29 +5478,29 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A26" s="31" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C26" s="17"/>
       <c r="D26" s="17"/>
       <c r="E26" s="18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F26" s="19"/>
       <c r="G26" s="30" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H26" s="21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I26" s="22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J26" s="19"/>
       <c r="K26" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L26" s="23" t="n">
         <f aca="false">MAX(DATE(2026,10,21),IF(COUNT(O24)=0,0,MAX(O24)+1))</f>
@@ -5583,10 +5583,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="35" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C27" s="37"/>
       <c r="D27" s="37"/>
@@ -5597,7 +5597,7 @@
       <c r="I27" s="38"/>
       <c r="J27" s="38"/>
       <c r="K27" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L27" s="39" t="n">
         <v>46319</v>
@@ -5948,7 +5948,7 @@
     </row>
     <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
@@ -6032,15 +6032,15 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
       <c r="E30" s="18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F30" s="19"/>
       <c r="G30" s="20" t="s">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="J30" s="19"/>
       <c r="K30" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L30" s="23" t="n">
         <v>46327</v>
@@ -6137,15 +6137,15 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B31" s="32" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
       <c r="E31" s="18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F31" s="19"/>
       <c r="G31" s="20" t="s">
@@ -6155,11 +6155,11 @@
         <v>31</v>
       </c>
       <c r="I31" s="22" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="J31" s="19"/>
       <c r="K31" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L31" s="23" t="n">
         <f aca="false">IF(COUNT(L32,L33)=0,"",MIN(L32,L33))</f>
@@ -6167,12 +6167,12 @@
       </c>
       <c r="M31" s="24" t="n">
         <f aca="false">IF(AND(ISNUMBER(L31),ISNUMBER(O31)),O31-L31+1,"")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23" t="n">
         <f aca="false">IF(COUNT(O32,O33)=0,"",MAX(O32,O33))</f>
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="P31" s="22"/>
       <c r="Q31" s="17"/>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="J32" s="19"/>
       <c r="K32" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L32" s="23" t="n">
         <v>46317</v>
@@ -6365,14 +6365,14 @@
         <v>31</v>
       </c>
       <c r="I33" s="22" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="J33" s="19"/>
       <c r="K33" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L33" s="23" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="M33" s="24" t="n">
         <v>1</v>
@@ -6380,7 +6380,7 @@
       <c r="N33" s="23"/>
       <c r="O33" s="23" t="n">
         <f aca="false">IF(ISNUMBER(L33),L33+M33-1,"")</f>
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="P33" s="22" t="s">
         <v>41</v>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="J34" s="19"/>
       <c r="K34" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L34" s="23" t="n">
         <f aca="false">IF(COUNT(L35,L36,L37,L38,L39,L40,L41,L42)=0,"",MIN(L35,L36,L37,L38,L39,L40,L41,L42))</f>
@@ -6572,14 +6572,14 @@
         <v>30</v>
       </c>
       <c r="H35" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I35" s="22" t="s">
         <v>32</v>
       </c>
       <c r="J35" s="19"/>
       <c r="K35" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L35" s="23" t="n">
         <v>46321</v>
@@ -6677,14 +6677,14 @@
         <v>30</v>
       </c>
       <c r="H36" s="21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I36" s="22" t="s">
         <v>32</v>
       </c>
       <c r="J36" s="19"/>
       <c r="K36" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L36" s="23" t="n">
         <v>46316</v>
@@ -6784,11 +6784,11 @@
         <v>31</v>
       </c>
       <c r="I37" s="22" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="J37" s="19"/>
       <c r="K37" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L37" s="23" t="n">
         <f aca="false">MAX(DATE(2026,10,27),IF(COUNT(O35,O36)=0,0,MAX(O35,O36)+1))</f>
@@ -6887,14 +6887,14 @@
         <v>113</v>
       </c>
       <c r="H38" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I38" s="22" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="J38" s="19"/>
       <c r="K38" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L38" s="23" t="n">
         <f aca="false">MAX(DATE(2026,10,26),IF(COUNT(O35)=0,0,MAX(O35)+1))</f>
@@ -6993,14 +6993,14 @@
         <v>116</v>
       </c>
       <c r="H39" s="21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I39" s="22" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="J39" s="19"/>
       <c r="K39" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L39" s="23" t="n">
         <f aca="false">MAX(DATE(2026,10,26),IF(COUNT(O36)=0,0,MAX(O36)+1))</f>
@@ -7104,11 +7104,9 @@
       <c r="I40" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="J40" s="34" t="s">
-        <v>75</v>
-      </c>
+      <c r="J40" s="19"/>
       <c r="K40" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L40" s="23" t="n">
         <f aca="false">MAX(DATE(2026,11,1),IF(COUNT(O38)=0,0,MAX(O38)+1))</f>
@@ -7210,13 +7208,13 @@
         <v>132</v>
       </c>
       <c r="I41" s="22" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="J41" s="34" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L41" s="23" t="n">
         <f aca="false">MAX(DATE(2026,11,1),IF(COUNT(O39)=0,0,MAX(O39)+1))</f>
@@ -7322,7 +7320,7 @@
       </c>
       <c r="J42" s="19"/>
       <c r="K42" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L42" s="23" t="n">
         <f aca="false">MAX(DATE(2026,11,1),IF(COUNT(O40,O41)=0,0,MAX(O40,O41)+1))</f>
@@ -7428,7 +7426,7 @@
       </c>
       <c r="J43" s="19"/>
       <c r="K43" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L43" s="23" t="n">
         <f aca="false">IF(COUNT(L44,L45,L46,L47)=0,"",MIN(L44,L45,L46,L47))</f>
@@ -7533,7 +7531,7 @@
       </c>
       <c r="J44" s="19"/>
       <c r="K44" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L44" s="23" t="n">
         <v>46314</v>
@@ -7631,14 +7629,14 @@
         <v>143</v>
       </c>
       <c r="H45" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I45" s="22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J45" s="19"/>
       <c r="K45" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L45" s="23" t="n">
         <f aca="false">MAX(DATE(2026,10,21),IF(COUNT(O44)=0,0,MAX(O44)+1))</f>
@@ -7744,10 +7742,10 @@
         <v>54</v>
       </c>
       <c r="J46" s="34" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K46" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L46" s="23" t="n">
         <f aca="false">MAX(DATE(2026,11,1),IF(COUNT(O45)=0,0,MAX(O45)+1))</f>
@@ -7852,10 +7850,10 @@
         <v>54</v>
       </c>
       <c r="J47" s="34" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K47" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L47" s="23" t="n">
         <f aca="false">MAX(DATE(2026,11,1),IF(COUNT(O45)=0,0,MAX(O45)+1))</f>
@@ -7961,7 +7959,7 @@
       </c>
       <c r="J48" s="19"/>
       <c r="K48" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L48" s="23" t="n">
         <f aca="false">IF(COUNT(L49,L50,L51,L52)=0,"",MIN(L49,L50,L51,L52))</f>
@@ -8066,7 +8064,7 @@
       </c>
       <c r="J49" s="19"/>
       <c r="K49" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L49" s="23" t="n">
         <v>46314</v>
@@ -8164,14 +8162,14 @@
         <v>166</v>
       </c>
       <c r="H50" s="21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I50" s="22" t="s">
         <v>32</v>
       </c>
       <c r="J50" s="19"/>
       <c r="K50" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L50" s="23" t="n">
         <f aca="false">MAX(DATE(2026,10,24),IF(COUNT(O51,O52)=0,0,MAX(O51,O52)+1))</f>
@@ -8276,7 +8274,7 @@
       </c>
       <c r="J51" s="19"/>
       <c r="K51" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L51" s="23" t="n">
         <f aca="false">MAX(DATE(2026,10,22),IF(COUNT(O49)=0,0,MAX(O49)+1))</f>
@@ -8381,7 +8379,7 @@
       </c>
       <c r="J52" s="19"/>
       <c r="K52" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L52" s="23" t="n">
         <f aca="false">MAX(DATE(2026,10,22),IF(COUNT(O49)=0,0,MAX(O49)+1))</f>
@@ -8486,7 +8484,7 @@
       </c>
       <c r="J53" s="19"/>
       <c r="K53" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L53" s="23" t="n">
         <f aca="false">IF(COUNT(L54,L55,L59,L60,L61,L62)=0,"",MIN(L54,L55,L59,L60,L61,L62))</f>
@@ -8591,7 +8589,7 @@
       </c>
       <c r="J54" s="19"/>
       <c r="K54" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L54" s="23" t="n">
         <v>46323</v>
@@ -8696,7 +8694,7 @@
       </c>
       <c r="J55" s="19"/>
       <c r="K55" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L55" s="23" t="n">
         <f aca="false">IF(COUNT(L56,L57,L58)=0,"",MIN(L56,L57,L58))</f>
@@ -8794,14 +8792,14 @@
         <v>30</v>
       </c>
       <c r="H56" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I56" s="22" t="s">
         <v>32</v>
       </c>
       <c r="J56" s="19"/>
       <c r="K56" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L56" s="23" t="n">
         <v>46323</v>
@@ -8899,14 +8897,14 @@
         <v>30</v>
       </c>
       <c r="H57" s="21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I57" s="22" t="s">
         <v>32</v>
       </c>
       <c r="J57" s="19"/>
       <c r="K57" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L57" s="23" t="n">
         <v>46315</v>
@@ -9011,7 +9009,7 @@
       </c>
       <c r="J58" s="19"/>
       <c r="K58" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L58" s="23" t="n">
         <f aca="false">MAX(DATE(2026,10,30),IF(COUNT(O9,O10,O56,O57)=0,0,MAX(O9,O10,O56,O57)+1))</f>
@@ -9113,11 +9111,11 @@
         <v>31</v>
       </c>
       <c r="I59" s="22" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="J59" s="19"/>
       <c r="K59" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L59" s="23" t="n">
         <v>46322</v>
@@ -9222,7 +9220,7 @@
       </c>
       <c r="J60" s="19"/>
       <c r="K60" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L60" s="23" t="n">
         <v>46317</v>
@@ -9327,7 +9325,7 @@
       </c>
       <c r="J61" s="19"/>
       <c r="K61" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L61" s="23" t="n">
         <f aca="false">MAX(DATE(2026,10,28),IF(COUNT(O11,O12)=0,0,MAX(O11,O12)+1))</f>
@@ -9433,7 +9431,7 @@
       </c>
       <c r="J62" s="19"/>
       <c r="K62" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L62" s="23" t="n">
         <f aca="false">MAX(DATE(2026,10,28),IF(COUNT(O58)=0,0,MAX(O58)+1))</f>
@@ -9535,11 +9533,11 @@
         <v>31</v>
       </c>
       <c r="I63" s="22" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="J63" s="19"/>
       <c r="K63" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L63" s="23" t="n">
         <f aca="false">IF(COUNT(L64,L65)=0,"",MIN(L64,L65))</f>
@@ -9640,11 +9638,11 @@
         <v>31</v>
       </c>
       <c r="I64" s="22" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="J64" s="19"/>
       <c r="K64" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L64" s="23" t="n">
         <v>46323</v>
@@ -9745,11 +9743,11 @@
         <v>31</v>
       </c>
       <c r="I65" s="22" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="J65" s="19"/>
       <c r="K65" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L65" s="23" t="n">
         <v>46323</v>
@@ -9850,11 +9848,11 @@
         <v>31</v>
       </c>
       <c r="I66" s="22" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="J66" s="19"/>
       <c r="K66" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L66" s="23" t="n">
         <v>46321</v>
@@ -9937,7 +9935,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="35" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B67" s="36" t="s">
         <v>218</v>
@@ -9951,7 +9949,7 @@
       <c r="I67" s="38"/>
       <c r="J67" s="38"/>
       <c r="K67" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L67" s="39" t="n">
         <v>46329</v>
@@ -10386,7 +10384,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="35" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B70" s="36" t="s">
         <v>220</v>
@@ -11270,7 +11268,7 @@
         <v>243</v>
       </c>
       <c r="H77" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I77" s="22" t="s">
         <v>54</v>
@@ -11378,7 +11376,7 @@
         <v>248</v>
       </c>
       <c r="H78" s="21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I78" s="22" t="s">
         <v>54</v>
@@ -15025,7 +15023,7 @@
     </row>
     <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="56" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8" s="57" t="s">
         <v>318</v>
@@ -15043,13 +15041,13 @@
     </row>
     <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="56" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C9" s="57" t="s">
         <v>322</v>
       </c>
       <c r="D9" s="59" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E9" s="58" t="s">
         <v>323</v>
@@ -15122,7 +15120,7 @@
     </row>
     <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="56" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C17" s="57" t="s">
         <v>333</v>
@@ -15140,7 +15138,7 @@
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="56" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C18" s="57" t="s">
         <v>336</v>
@@ -15256,7 +15254,7 @@
     </row>
     <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="65" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C5" s="66" t="s">
         <v>353</v>
@@ -15264,7 +15262,7 @@
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="65" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C6" s="66" t="s">
         <v>354</v>

--- a/gantt-piloto-2026-10-29.xlsx
+++ b/gantt-piloto-2026-10-29.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="355">
   <si>
     <t xml:space="preserve">Grupo Bimbo × Uvicuo · Plan de arranque del piloto de peajes</t>
   </si>
@@ -635,7 +635,7 @@
     <t xml:space="preserve">Validación de la lista · Bimbo</t>
   </si>
   <si>
-    <t xml:space="preserve">La operación de Bimbo Sureste confirma qué operadores y qué unidades de la lista entran al piloto.</t>
+    <t xml:space="preserve">Giselle (Bimbo Sureste) validó y devolvió las listas: operadores de Región Sur (161, con sus altas marcadas) y unidades RS con su centro/ubicación.</t>
   </si>
   <si>
     <t xml:space="preserve">Cada jefe de transporte revisa al tener acceso a la plataforma</t>
@@ -7632,7 +7632,7 @@
         <v>76</v>
       </c>
       <c r="I45" s="22" t="s">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="J45" s="19"/>
       <c r="K45" s="15" t="s">
@@ -7643,11 +7643,11 @@
         <v>46317</v>
       </c>
       <c r="M45" s="24" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N45" s="23"/>
       <c r="O45" s="23" t="n">
-        <v>46319</v>
+        <v>46324</v>
       </c>
       <c r="P45" s="22" t="s">
         <v>34</v>
@@ -7741,9 +7741,7 @@
       <c r="I46" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="J46" s="34" t="s">
-        <v>76</v>
-      </c>
+      <c r="J46" s="19"/>
       <c r="K46" s="15" t="s">
         <v>100</v>
       </c>
@@ -7849,9 +7847,7 @@
       <c r="I47" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="J47" s="34" t="s">
-        <v>76</v>
-      </c>
+      <c r="J47" s="19"/>
       <c r="K47" s="15" t="s">
         <v>100</v>
       </c>
